--- a/artfynd/A 17982-2023 artfynd.xlsx
+++ b/artfynd/A 17982-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17982-2023 artfynd.xlsx
+++ b/artfynd/A 17982-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>104715547</v>
       </c>
       <c r="B2" t="n">
-        <v>100520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102816</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>701686.7733299024</v>
+        <v>701687</v>
       </c>
       <c r="R2" t="n">
-        <v>6349412.081638243</v>
+        <v>6349412</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2008-07-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-07-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>104715564</v>
       </c>
       <c r="B3" t="n">
-        <v>108203</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110691</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701578.2811656439</v>
+        <v>701578</v>
       </c>
       <c r="R3" t="n">
-        <v>6349321.117740908</v>
+        <v>6349321</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,19 +854,9 @@
           <t>2008-07-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-07-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -930,12 +900,7 @@
         <v>104715561</v>
       </c>
       <c r="B4" t="n">
-        <v>107008</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>701578.2811656439</v>
+        <v>701578</v>
       </c>
       <c r="R4" t="n">
-        <v>6349321.117740908</v>
+        <v>6349321</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,19 +974,9 @@
           <t>2008-07-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2008-07-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 17982-2023 artfynd.xlsx
+++ b/artfynd/A 17982-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104715547</v>
       </c>
       <c r="B2" t="n">
-        <v>102816</v>
+        <v>102824</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>104715564</v>
       </c>
       <c r="B3" t="n">
-        <v>110691</v>
+        <v>110700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>104715561</v>
       </c>
       <c r="B4" t="n">
-        <v>109453</v>
+        <v>109462</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 17982-2023 artfynd.xlsx
+++ b/artfynd/A 17982-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104715547</v>
       </c>
       <c r="B2" t="n">
-        <v>102824</v>
+        <v>102834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>104715564</v>
       </c>
       <c r="B3" t="n">
-        <v>110700</v>
+        <v>110713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>104715561</v>
       </c>
       <c r="B4" t="n">
-        <v>109462</v>
+        <v>109475</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 17982-2023 artfynd.xlsx
+++ b/artfynd/A 17982-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104715547</v>
       </c>
       <c r="B2" t="n">
-        <v>102834</v>
+        <v>102840</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>104715564</v>
       </c>
       <c r="B3" t="n">
-        <v>110713</v>
+        <v>110722</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>104715561</v>
       </c>
       <c r="B4" t="n">
-        <v>109475</v>
+        <v>109484</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 17982-2023 artfynd.xlsx
+++ b/artfynd/A 17982-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104715547</v>
       </c>
       <c r="B2" t="n">
-        <v>102840</v>
+        <v>102841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>104715564</v>
       </c>
       <c r="B3" t="n">
-        <v>110722</v>
+        <v>110727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>104715561</v>
       </c>
       <c r="B4" t="n">
-        <v>109484</v>
+        <v>109489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 17982-2023 artfynd.xlsx
+++ b/artfynd/A 17982-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104715547</v>
       </c>
       <c r="B2" t="n">
-        <v>102841</v>
+        <v>102868</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>104715564</v>
       </c>
       <c r="B3" t="n">
-        <v>110727</v>
+        <v>110755</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>104715561</v>
       </c>
       <c r="B4" t="n">
-        <v>109489</v>
+        <v>109517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 17982-2023 artfynd.xlsx
+++ b/artfynd/A 17982-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104715547</v>
       </c>
       <c r="B2" t="n">
-        <v>102868</v>
+        <v>102874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>104715564</v>
       </c>
       <c r="B3" t="n">
-        <v>110755</v>
+        <v>110761</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>104715561</v>
       </c>
       <c r="B4" t="n">
-        <v>109517</v>
+        <v>109523</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 17982-2023 artfynd.xlsx
+++ b/artfynd/A 17982-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104715547</v>
       </c>
       <c r="B2" t="n">
-        <v>102874</v>
+        <v>102881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>104715564</v>
       </c>
       <c r="B3" t="n">
-        <v>110761</v>
+        <v>110768</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>104715561</v>
       </c>
       <c r="B4" t="n">
-        <v>109523</v>
+        <v>109530</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 17982-2023 artfynd.xlsx
+++ b/artfynd/A 17982-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104715547</v>
       </c>
       <c r="B2" t="n">
-        <v>102881</v>
+        <v>102885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>104715564</v>
       </c>
       <c r="B3" t="n">
-        <v>110768</v>
+        <v>110772</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>104715561</v>
       </c>
       <c r="B4" t="n">
-        <v>109530</v>
+        <v>109534</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 17982-2023 artfynd.xlsx
+++ b/artfynd/A 17982-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104715547</v>
       </c>
       <c r="B2" t="n">
-        <v>102885</v>
+        <v>102892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>104715564</v>
       </c>
       <c r="B3" t="n">
-        <v>110772</v>
+        <v>110780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>104715561</v>
       </c>
       <c r="B4" t="n">
-        <v>109534</v>
+        <v>109542</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 17982-2023 artfynd.xlsx
+++ b/artfynd/A 17982-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104715547</v>
       </c>
       <c r="B2" t="n">
-        <v>102895</v>
+        <v>102900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>104715564</v>
       </c>
       <c r="B3" t="n">
-        <v>110783</v>
+        <v>110788</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>104715561</v>
       </c>
       <c r="B4" t="n">
-        <v>109545</v>
+        <v>109550</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 17982-2023 artfynd.xlsx
+++ b/artfynd/A 17982-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104715547</v>
       </c>
       <c r="B2" t="n">
-        <v>102900</v>
+        <v>102908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>104715564</v>
       </c>
       <c r="B3" t="n">
-        <v>110788</v>
+        <v>110796</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>104715561</v>
       </c>
       <c r="B4" t="n">
-        <v>109550</v>
+        <v>109558</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 17982-2023 artfynd.xlsx
+++ b/artfynd/A 17982-2023 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104715547</v>
+        <v>104715564</v>
       </c>
       <c r="B2" t="n">
-        <v>102908</v>
+        <v>111399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223248</v>
+        <v>219716</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lundalm</t>
+          <t>Krusfrö</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ulmus minor</t>
+          <t>Selinum carvifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Mill.</t>
+          <t>(L.) L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Likmide 430 m VSV, Gtl</t>
+          <t>Likmide 600 m VSV, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>701687</v>
+        <v>701578</v>
       </c>
       <c r="R2" t="n">
-        <v>6349412</v>
+        <v>6349321</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>xkoord = 1653180, ykoord = 6349229</t>
+          <t>xkoord = 1653075, ykoord = 6349130</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Lövskog, glänta</t>
+          <t>Lövskogsglänta mellan körväg och fuktmark.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104715564</v>
+        <v>104715561</v>
       </c>
       <c r="B3" t="n">
-        <v>110796</v>
+        <v>110117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,24 +797,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219716</v>
+        <v>220320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Krusfrö</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Selinum carvifolia</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Likmide 600 m VSV, Gtl</t>
@@ -861,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>xkoord = 1653075, ykoord = 6349130</t>
+          <t>93 stänglat i 47 grupper, + 1 steril rosett. xkoord = 1653075, ykoord = 6349130</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,54 +906,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104715561</v>
+        <v>104715547</v>
       </c>
       <c r="B4" t="n">
-        <v>109558</v>
+        <v>103408</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220320</v>
+        <v>223248</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Lundalm</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Ulmus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Likmide 600 m VSV, Gtl</t>
+          <t>Likmide 430 m VSV, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>701578</v>
+        <v>701687</v>
       </c>
       <c r="R4" t="n">
-        <v>6349321</v>
+        <v>6349412</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>93 stänglat i 47 grupper, + 1 steril rosett. xkoord = 1653075, ykoord = 6349130</t>
+          <t>xkoord = 1653180, ykoord = 6349229</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,7 +995,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Lövskogsglänta mellan körväg och fuktmark.</t>
+          <t>Lövskog, glänta</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 17982-2023 artfynd.xlsx
+++ b/artfynd/A 17982-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104715564</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104715561</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,8 +1029,18 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104715547</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>